--- a/public/templates/Design_Schedule_Template.xlsx
+++ b/public/templates/Design_Schedule_Template.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Design Schedule" sheetId="2" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="false" localSheetId="1" name="_xlnm.Print_Area" vbProcedure="false">'Design Schedule'!$A$1:$H$29</definedName>
+    <definedName function="false" hidden="false" localSheetId="1" name="_xlnm.Print_Area" vbProcedure="false">'Design Schedule'!$A$1:$F$30</definedName>
     <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">'Design Schedule Details'!$A$1:$B$14</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
@@ -25,12 +25,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="59">
   <si>
     <t xml:space="preserve">THE HABITAINER — DESIGN SCHEDULE TEMPLATE  |  Fill and upload to HStack</t>
   </si>
   <si>
-    <t xml:space="preserve">Version 1.0  |  This file is downloaded from HStack when a project reaches Handover to Design. Project fields (grey) are pre-filled from the app. Fill white fields only. Upload via Projects → [Project] → Design Schedule → Upload Design Schedule.</t>
+    <t xml:space="preserve">Version 2.0  |  This file is downloaded from HStack when a project reaches Handover to Design. Project fields (grey) are pre-filled from the app. Fill white fields only. Upload via Projects → [Project] → Design Schedule → Upload Design Schedule.</t>
   </si>
   <si>
     <t xml:space="preserve">  🔒 Grey = Pre-filled from HStack (do not change)      ✏ White = Fill this in      🔽 = Dropdown — click to select</t>
@@ -42,13 +42,13 @@
     <t xml:space="preserve">Project Code</t>
   </si>
   <si>
-    <t xml:space="preserve">PEBB/26/3AC</t>
+    <t xml:space="preserve">MAHE/26/7E9</t>
   </si>
   <si>
     <t xml:space="preserve">Project Name</t>
   </si>
   <si>
-    <t xml:space="preserve">Pebble Beach House</t>
+    <t xml:space="preserve">Mahesh Villa</t>
   </si>
   <si>
     <t xml:space="preserve">Division</t>
@@ -66,7 +66,7 @@
     <t xml:space="preserve">Client Name</t>
   </si>
   <si>
-    <t xml:space="preserve">Thakur Bhakshani</t>
+    <t xml:space="preserve">Mahesh Veerappa</t>
   </si>
   <si>
     <t xml:space="preserve">  DESIGN TEAM ASSIGNMENT</t>
@@ -90,10 +90,10 @@
     <t xml:space="preserve">⚠ Sale Agreement and Scope of Work status are NOT filled here — they're tracked on the Pre-Production Checklist (gates C-3+C-4) and update automatically. Quotation and Negotiation stages belong to the Sales pipeline, not this sheet.</t>
   </si>
   <si>
-    <t xml:space="preserve">DESIGN SCHEDULE  |  Fill Planned Dates per Stage</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ℹ Fill Planned Start &amp; Planned End for every stage that applies. Use DD/MM/YYYY format. Proof Type is pre-set per HStack's rule (pre-deal stages accept a WhatsApp screenshot; post-deal stages require formal email confirmation) — do not change. Mark N/A in Notes if a stage doesn't apply to this project.</t>
+    <t xml:space="preserve">DESIGN SCHEDULE  |  Fill Planned Date per Stage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ℹ Fill the Planned Date for every stage that applies — this is the target date the stage should be complete by. Use DD/MM/YYYY format. Proof Type is pre-set per HStack's rule (pre-deal stages accept a WhatsApp screenshot; post-deal stages require formal email confirmation) — do not change. Mark N/A in Notes if a stage doesn't apply to this project.</t>
   </si>
   <si>
     <t xml:space="preserve">  🟢 Design Team fills dates     🔵 Rows marked 'Combined Gate' club two checkpoints into one row, same pattern as the Sale Agreement + Scope of Work gate</t>
@@ -108,18 +108,10 @@
     <t xml:space="preserve">Section</t>
   </si>
   <si>
-    <t xml:space="preserve">Planned Start
+    <t xml:space="preserve">Planned Date
 (DD/MM/YYYY)</t>
   </si>
   <si>
-    <t xml:space="preserve">Planned End
-(DD/MM/YYYY)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Duration
-(Days, auto)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Proof Type</t>
   </si>
   <si>
@@ -210,7 +202,7 @@
     <t xml:space="preserve">Handover to Planning</t>
   </si>
   <si>
-    <t xml:space="preserve">Combined Gate rows (Row 9, Row 10) mark BOTH checkpoints complete when this row's dates are filled — same behaviour as the Sale Agreement + Scope of Work combined gate elsewhere in HStack. Do not split these into two rows.</t>
+    <t xml:space="preserve">Combined Gate rows (Row 9, Row 10) mark BOTH checkpoints complete when this row's date is filled — same behaviour as the Sale Agreement + Scope of Work combined gate elsewhere in HStack. Do not split these into two rows.</t>
   </si>
 </sst>
 </file>
@@ -220,7 +212,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -284,14 +276,6 @@
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <i val="true"/>
-      <sz val="10"/>
-      <color rgb="FF777777"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -378,7 +362,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -419,10 +403,6 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -449,7 +429,7 @@
       <rgbColor rgb="FF800080"/>
       <rgbColor rgb="FF008080"/>
       <rgbColor rgb="FFB0B0B0"/>
-      <rgbColor rgb="FF777777"/>
+      <rgbColor rgb="FF808080"/>
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FFE8E8E8"/>
@@ -808,14 +788,15 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:H28"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="46"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="4" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="30"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -827,8 +808,6 @@
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
     </row>
     <row r="2" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
@@ -839,8 +818,6 @@
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
@@ -851,8 +828,6 @@
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
       <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="s">
@@ -873,454 +848,343 @@
       <c r="F4" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="G4" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="H4" s="9" t="s">
-        <v>31</v>
-      </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="n">
         <v>1</v>
       </c>
       <c r="B5" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="D5" s="8"/>
+      <c r="E5" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="C5" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="10" t="str">
-        <f aca="false">IF(AND(D5&lt;&gt;"",E5&lt;&gt;""),E5-D5,"")</f>
-        <v/>
-      </c>
-      <c r="G5" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="H5" s="8"/>
+      <c r="F5" s="8"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="n">
         <v>2</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D6" s="8"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="10" t="str">
-        <f aca="false">IF(AND(D6&lt;&gt;"",E6&lt;&gt;""),E6-D6,"")</f>
-        <v/>
-      </c>
-      <c r="G6" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="H6" s="8"/>
+      <c r="E6" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="F6" s="8"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="n">
         <v>3</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="10" t="str">
-        <f aca="false">IF(AND(D7&lt;&gt;"",E7&lt;&gt;""),E7-D7,"")</f>
-        <v/>
-      </c>
-      <c r="G7" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="H7" s="8"/>
+      <c r="E7" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="F7" s="8"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="n">
         <v>4</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D8" s="8"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="10" t="str">
-        <f aca="false">IF(AND(D8&lt;&gt;"",E8&lt;&gt;""),E8-D8,"")</f>
-        <v/>
-      </c>
-      <c r="G8" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="H8" s="8"/>
+      <c r="E8" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="F8" s="8"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="n">
         <v>5</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D9" s="8"/>
-      <c r="E9" s="8"/>
-      <c r="F9" s="10" t="str">
-        <f aca="false">IF(AND(D9&lt;&gt;"",E9&lt;&gt;""),E9-D9,"")</f>
-        <v/>
-      </c>
-      <c r="G9" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="H9" s="8"/>
+      <c r="E9" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="F9" s="8"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="n">
         <v>6</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="10" t="str">
-        <f aca="false">IF(AND(D10&lt;&gt;"",E10&lt;&gt;""),E10-D10,"")</f>
-        <v/>
-      </c>
-      <c r="G10" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="H10" s="8"/>
+      <c r="E10" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="F10" s="8"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="n">
         <v>7</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D11" s="8"/>
-      <c r="E11" s="8"/>
-      <c r="F11" s="10" t="str">
-        <f aca="false">IF(AND(D11&lt;&gt;"",E11&lt;&gt;""),E11-D11,"")</f>
-        <v/>
-      </c>
-      <c r="G11" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="H11" s="8"/>
+      <c r="E11" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="F11" s="8"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="n">
         <v>8</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D12" s="8"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="10" t="str">
-        <f aca="false">IF(AND(D12&lt;&gt;"",E12&lt;&gt;""),E12-D12,"")</f>
-        <v/>
-      </c>
-      <c r="G12" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="H12" s="8"/>
+      <c r="E12" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="F12" s="8"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="n">
         <v>9</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D13" s="8"/>
-      <c r="E13" s="8"/>
-      <c r="F13" s="10" t="str">
-        <f aca="false">IF(AND(D13&lt;&gt;"",E13&lt;&gt;""),E13-D13,"")</f>
-        <v/>
-      </c>
-      <c r="G13" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="H13" s="8"/>
+      <c r="E13" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="F13" s="8"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="n">
         <v>10</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D14" s="8"/>
-      <c r="E14" s="8"/>
-      <c r="F14" s="10" t="str">
-        <f aca="false">IF(AND(D14&lt;&gt;"",E14&lt;&gt;""),E14-D14,"")</f>
-        <v/>
-      </c>
-      <c r="G14" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="H14" s="8"/>
+      <c r="E14" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="F14" s="8"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="n">
         <v>11</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D15" s="8"/>
-      <c r="E15" s="8"/>
-      <c r="F15" s="10" t="str">
-        <f aca="false">IF(AND(D15&lt;&gt;"",E15&lt;&gt;""),E15-D15,"")</f>
-        <v/>
-      </c>
-      <c r="G15" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="H15" s="8"/>
+      <c r="E15" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="F15" s="8"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="n">
         <v>12</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D16" s="8"/>
-      <c r="E16" s="8"/>
-      <c r="F16" s="10" t="str">
-        <f aca="false">IF(AND(D16&lt;&gt;"",E16&lt;&gt;""),E16-D16,"")</f>
-        <v/>
-      </c>
-      <c r="G16" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="H16" s="8"/>
+      <c r="E16" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="F16" s="8"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="n">
         <v>13</v>
       </c>
       <c r="B17" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="D17" s="8"/>
+      <c r="E17" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="C17" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="D17" s="8"/>
-      <c r="E17" s="8"/>
-      <c r="F17" s="10" t="str">
-        <f aca="false">IF(AND(D17&lt;&gt;"",E17&lt;&gt;""),E17-D17,"")</f>
-        <v/>
-      </c>
-      <c r="G17" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="H17" s="8"/>
+      <c r="F17" s="8"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="n">
         <v>14</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D18" s="8"/>
-      <c r="E18" s="8"/>
-      <c r="F18" s="10" t="str">
-        <f aca="false">IF(AND(D18&lt;&gt;"",E18&lt;&gt;""),E18-D18,"")</f>
-        <v/>
-      </c>
-      <c r="G18" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="H18" s="8"/>
+      <c r="E18" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="F18" s="8"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="6" t="n">
         <v>15</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D19" s="8"/>
-      <c r="E19" s="8"/>
-      <c r="F19" s="10" t="str">
-        <f aca="false">IF(AND(D19&lt;&gt;"",E19&lt;&gt;""),E19-D19,"")</f>
-        <v/>
-      </c>
-      <c r="G19" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="H19" s="8"/>
+      <c r="E19" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="F19" s="8"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="6" t="n">
         <v>16</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D20" s="8"/>
-      <c r="E20" s="8"/>
-      <c r="F20" s="10" t="str">
-        <f aca="false">IF(AND(D20&lt;&gt;"",E20&lt;&gt;""),E20-D20,"")</f>
-        <v/>
-      </c>
-      <c r="G20" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="H20" s="8"/>
+      <c r="E20" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="F20" s="8"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="6" t="n">
         <v>17</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D21" s="8"/>
-      <c r="E21" s="8"/>
-      <c r="F21" s="10" t="str">
-        <f aca="false">IF(AND(D21&lt;&gt;"",E21&lt;&gt;""),E21-D21,"")</f>
-        <v/>
-      </c>
-      <c r="G21" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="H21" s="8"/>
+      <c r="E21" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="F21" s="8"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="6" t="n">
         <v>18</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D22" s="8"/>
-      <c r="E22" s="8"/>
-      <c r="F22" s="10" t="str">
-        <f aca="false">IF(AND(D22&lt;&gt;"",E22&lt;&gt;""),E22-D22,"")</f>
-        <v/>
-      </c>
-      <c r="G22" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="H22" s="8"/>
+      <c r="E22" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="F22" s="8"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="6" t="n">
         <v>19</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D23" s="8"/>
-      <c r="E23" s="8"/>
-      <c r="F23" s="10" t="str">
-        <f aca="false">IF(AND(D23&lt;&gt;"",E23&lt;&gt;""),E23-D23,"")</f>
-        <v/>
-      </c>
-      <c r="G23" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="H23" s="8"/>
+      <c r="E23" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="F23" s="8"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="6" t="n">
         <v>20</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D24" s="8"/>
-      <c r="E24" s="8"/>
-      <c r="F24" s="10" t="str">
-        <f aca="false">IF(AND(D24&lt;&gt;"",E24&lt;&gt;""),E24-D24,"")</f>
-        <v/>
-      </c>
-      <c r="G24" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="H24" s="8"/>
+      <c r="E24" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="F24" s="8"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="6" t="n">
         <v>21</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D25" s="8"/>
-      <c r="E25" s="8"/>
-      <c r="F25" s="10" t="str">
-        <f aca="false">IF(AND(D25&lt;&gt;"",E25&lt;&gt;""),E25-D25,"")</f>
-        <v/>
-      </c>
-      <c r="G25" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="H25" s="8" t="s">
-        <v>58</v>
+      <c r="E25" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="F25" s="8" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1328,40 +1192,33 @@
         <v>22</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D26" s="8"/>
-      <c r="E26" s="8"/>
-      <c r="F26" s="10" t="str">
-        <f aca="false">IF(AND(D26&lt;&gt;"",E26&lt;&gt;""),E26-D26,"")</f>
-        <v/>
-      </c>
-      <c r="G26" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="H26" s="8"/>
+      <c r="E26" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="F26" s="8"/>
     </row>
     <row r="28" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
       <c r="D28" s="2"/>
       <c r="E28" s="2"/>
       <c r="F28" s="2"/>
-      <c r="G28" s="2"/>
-      <c r="H28" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A28:H28"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A28:F28"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
